--- a/Result/profitability/6510.xlsx
+++ b/Result/profitability/6510.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM51"/>
+  <dimension ref="A1:AM52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6907,6 +6907,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1640</v>
+      </c>
+      <c r="D52" t="n">
+        <v>697</v>
+      </c>
+      <c r="E52" t="n">
+        <v>943</v>
+      </c>
+      <c r="F52" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="G52" t="n">
+        <v>570</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>34.75%</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>26</v>
+      </c>
+      <c r="J52" t="n">
+        <v>596</v>
+      </c>
+      <c r="K52" t="n">
+        <v>494</v>
+      </c>
+      <c r="L52" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="M52" t="n">
+        <v>8.61875</v>
+      </c>
+      <c r="N52" t="n">
+        <v>55.61875</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
+      </c>
+      <c r="V52" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W52" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0.4400767018216682</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.01321120310022894</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.282674772036474</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.670000000000002</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.02990152193375106</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK52" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
